--- a/outputs/reports/stacked_ensemble/evaluation.xlsx
+++ b/outputs/reports/stacked_ensemble/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9364349659534755</v>
+        <v>0.9547509408561026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03837081302091524</v>
+        <v>0.06386020651310564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9420849420849421</v>
+        <v>0.9469964664310954</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07373828951344817</v>
+        <v>0.1196517598035568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.936419750947032</v>
+        <v>0.9547762024442185</v>
       </c>
       <c r="G2" t="n">
-        <v>270188</v>
+        <v>248829</v>
       </c>
       <c r="H2" t="n">
-        <v>18345</v>
+        <v>11786</v>
       </c>
       <c r="I2" t="n">
         <v>45</v>
       </c>
       <c r="J2" t="n">
-        <v>732</v>
+        <v>804</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9783329722782055</v>
+        <v>0.9822966410407276</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7070085884540985</v>
+        <v>0.8596319260463616</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,32 +562,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>상위1%양성포착비율(top_1pct_recall)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>상위5%건수(top_5pct_count)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>상위5%양성비율(top_5pct_positive_rate)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>상위5%리프트(top_5pct_lift)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>상위5%양성포착비율(top_5pct_recall)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>상위10%건수(top_10pct_count)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>상위10%양성비율(top_10pct_positive_rate)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>상위10%리프트(top_10pct_lift)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>상위10%양성포착비율(top_10pct_recall)</t>
         </is>
       </c>
     </row>
@@ -598,34 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.241534208707671</v>
+        <v>0.2978967495219885</v>
       </c>
       <c r="E2" t="n">
-        <v>89.93341302601841</v>
+        <v>91.74237422499081</v>
       </c>
       <c r="F2" t="n">
-        <v>14466</v>
+        <v>0.917550058892815</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05053228259366791</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>18.81530846483149</v>
+        <v>0.06164907449900566</v>
       </c>
       <c r="I2" t="n">
-        <v>28931</v>
+        <v>18.98588176066904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02554353461684698</v>
+        <v>0.9493521790341578</v>
       </c>
       <c r="K2" t="n">
-        <v>9.51093951093951</v>
+        <v>26147</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03101694267028722</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.552195404409868</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9552414605418139</v>
       </c>
     </row>
   </sheetData>
@@ -676,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>125270</v>
+        <v>144571</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>7.982757244352199e-05</v>
+        <v>7.60871820766267e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -695,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79807</v>
+        <v>64688</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001754232084904833</v>
+        <v>0.0002937175364828098</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -714,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35154</v>
+        <v>22366</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001706775900324288</v>
+        <v>0.0003129750514173299</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -733,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18830</v>
+        <v>10874</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004248539564524695</v>
+        <v>0.0004598123965422108</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -752,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11131</v>
+        <v>6356</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0006288743149761927</v>
+        <v>0.0004719949653870359</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -771,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7204</v>
+        <v>4267</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000694058856191005</v>
+        <v>0.0007030700726505742</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -790,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4693</v>
+        <v>2900</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002343916471340294</v>
+        <v>0.002758620689655172</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -809,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3151</v>
+        <v>2101</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003808314820691844</v>
+        <v>0.003807710613993336</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -828,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2004</v>
+        <v>1365</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007984031936127744</v>
+        <v>0.008058608058608059</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -847,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2066</v>
+        <v>1976</v>
       </c>
       <c r="C11" t="n">
-        <v>688</v>
+        <v>774</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3330106485963214</v>
+        <v>0.3917004048582996</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
